--- a/AAII_Financials/Quarterly/HCMA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HCMA_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="92">
   <si>
     <t>HCMA</t>
   </si>
@@ -656,63 +656,64 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
@@ -728,8 +729,11 @@
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -775,8 +779,11 @@
       <c r="Q8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -822,8 +829,11 @@
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -869,8 +879,11 @@
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -888,8 +901,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -935,8 +949,11 @@
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -982,8 +999,11 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1029,8 +1049,11 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1076,8 +1099,11 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1092,37 +1118,38 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E17" s="3">
         <v>800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>400</v>
       </c>
-      <c r="J17" s="3">
-        <v>0</v>
-      </c>
       <c r="K17" s="3">
         <v>0</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
+      <c r="L17" s="3">
+        <v>0</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
@@ -1139,8 +1166,11 @@
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1148,28 +1178,28 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F18" s="3">
         <v>-1600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-400</v>
       </c>
-      <c r="J18" s="3">
-        <v>0</v>
-      </c>
       <c r="K18" s="3">
         <v>0</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
+      <c r="L18" s="3">
+        <v>0</v>
       </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
@@ -1186,8 +1216,11 @@
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1205,8 +1238,9 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1214,28 +1248,28 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F20" s="3">
         <v>2400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>3800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>3100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>7500</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
+      <c r="L20" s="3">
+        <v>0</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
@@ -1252,8 +1286,11 @@
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1299,8 +1336,11 @@
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1346,37 +1386,40 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E23" s="3">
         <v>1300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>3000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>7100</v>
       </c>
-      <c r="J23" s="3">
-        <v>0</v>
-      </c>
       <c r="K23" s="3">
         <v>0</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
+      <c r="L23" s="3">
+        <v>0</v>
       </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
@@ -1393,8 +1436,11 @@
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1440,8 +1486,11 @@
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1487,37 +1536,40 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E26" s="3">
         <v>1300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>7100</v>
       </c>
-      <c r="J26" s="3">
-        <v>0</v>
-      </c>
       <c r="K26" s="3">
         <v>0</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
+      <c r="L26" s="3">
+        <v>0</v>
       </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
@@ -1534,37 +1586,40 @@
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E27" s="3">
         <v>1300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>7100</v>
       </c>
-      <c r="J27" s="3">
-        <v>0</v>
-      </c>
       <c r="K27" s="3">
         <v>0</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
+      <c r="L27" s="3">
+        <v>0</v>
       </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
@@ -1581,8 +1636,11 @@
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1628,8 +1686,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1675,8 +1736,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1722,8 +1786,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1769,8 +1836,11 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1778,28 +1848,28 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F32" s="3">
         <v>-2400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-3800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-3100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-7500</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
+      <c r="L32" s="3">
+        <v>0</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
@@ -1816,37 +1886,40 @@
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E33" s="3">
         <v>1300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>7100</v>
       </c>
-      <c r="J33" s="3">
-        <v>0</v>
-      </c>
       <c r="K33" s="3">
         <v>0</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
+      <c r="L33" s="3">
+        <v>0</v>
       </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
@@ -1863,8 +1936,11 @@
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1910,37 +1986,40 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E35" s="3">
         <v>1300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>7100</v>
       </c>
-      <c r="J35" s="3">
-        <v>0</v>
-      </c>
       <c r="K35" s="3">
         <v>0</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
+      <c r="L35" s="3">
+        <v>0</v>
       </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
@@ -1957,43 +2036,46 @@
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2009,8 +2091,11 @@
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2028,8 +2113,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2047,8 +2133,9 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2056,28 +2143,28 @@
         <v>100</v>
       </c>
       <c r="E41" s="3">
+        <v>100</v>
+      </c>
+      <c r="F41" s="3">
         <v>500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1200</v>
       </c>
-      <c r="J41" s="3">
-        <v>0</v>
-      </c>
       <c r="K41" s="3">
         <v>0</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
+      <c r="L41" s="3">
+        <v>0</v>
       </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
@@ -2094,8 +2181,11 @@
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2141,8 +2231,11 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2188,8 +2281,11 @@
       <c r="Q43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2235,8 +2331,11 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2244,23 +2343,23 @@
         <v>100</v>
       </c>
       <c r="E45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F45" s="3">
         <v>200</v>
       </c>
       <c r="G45" s="3">
+        <v>200</v>
+      </c>
+      <c r="H45" s="3">
         <v>300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>300</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2273,8 +2372,8 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3">
-        <v>0</v>
+      <c r="O45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P45" s="3">
         <v>0</v>
@@ -2282,37 +2381,40 @@
       <c r="Q45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>200</v>
+      </c>
+      <c r="E46" s="3">
         <v>300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1400</v>
       </c>
-      <c r="J46" s="3">
-        <v>0</v>
-      </c>
       <c r="K46" s="3">
         <v>0</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
+      <c r="L46" s="3">
+        <v>0</v>
       </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
@@ -2329,32 +2431,35 @@
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>44700</v>
+      </c>
+      <c r="E47" s="3">
         <v>43700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>300000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>297600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>295200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>293800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>293400</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2367,8 +2472,8 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -2376,8 +2481,11 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2423,8 +2531,11 @@
       <c r="Q48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2470,8 +2581,11 @@
       <c r="Q49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2517,8 +2631,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2564,8 +2681,11 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2575,26 +2695,26 @@
       <c r="E52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F52" s="3">
-        <v>0</v>
+      <c r="F52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G52" s="3">
         <v>0</v>
       </c>
       <c r="H52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I52" s="3">
         <v>100</v>
       </c>
       <c r="J52" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="K52" s="3">
         <v>300</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
+      <c r="L52" s="3">
+        <v>300</v>
       </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
@@ -2611,8 +2731,11 @@
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2658,37 +2781,40 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>44800</v>
+      </c>
+      <c r="E54" s="3">
         <v>43900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>300700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>298600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>296400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>295200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>294900</v>
-      </c>
-      <c r="J54" s="3">
-        <v>300</v>
       </c>
       <c r="K54" s="3">
         <v>300</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
+      <c r="L54" s="3">
+        <v>300</v>
       </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
@@ -2705,8 +2831,11 @@
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2724,8 +2853,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2743,8 +2873,9 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2790,19 +2921,22 @@
       <c r="Q57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E58" s="3">
         <v>400</v>
       </c>
-      <c r="E58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F58" s="3">
-        <v>0</v>
+      <c r="F58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G58" s="3">
         <v>0</v>
@@ -2814,13 +2948,13 @@
         <v>0</v>
       </c>
       <c r="J58" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="K58" s="3">
         <v>200</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
+      <c r="L58" s="3">
+        <v>200</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
@@ -2837,37 +2971,40 @@
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E59" s="3">
         <v>2900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>400</v>
-      </c>
-      <c r="J59" s="3">
-        <v>100</v>
       </c>
       <c r="K59" s="3">
         <v>100</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
+      <c r="L59" s="3">
+        <v>100</v>
       </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
@@ -2884,38 +3021,41 @@
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E60" s="3">
         <v>3300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>200</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2931,8 +3071,11 @@
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2978,8 +3121,11 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2987,23 +3133,23 @@
         <v>3500</v>
       </c>
       <c r="E62" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F62" s="3">
         <v>3800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>15700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>17000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>17900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>20600</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3016,8 +3162,8 @@
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
+      <c r="O62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P62" s="3">
         <v>0</v>
@@ -3025,8 +3171,11 @@
       <c r="Q62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3072,8 +3221,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3119,8 +3271,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3166,38 +3321,41 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E66" s="3">
         <v>6900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>17000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>17600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>18200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>21000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>200</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3213,8 +3371,11 @@
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3232,8 +3393,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3279,8 +3441,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3326,8 +3491,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3373,8 +3541,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3420,37 +3591,40 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-20400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-18400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-17500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-16000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-16400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-16800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-19300</v>
       </c>
-      <c r="J72" s="3">
-        <v>0</v>
-      </c>
       <c r="K72" s="3">
         <v>0</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
+      <c r="L72" s="3">
+        <v>0</v>
       </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
@@ -3467,8 +3641,11 @@
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3514,8 +3691,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3561,8 +3741,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3608,37 +3791,40 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>36100</v>
+      </c>
+      <c r="E76" s="3">
         <v>37100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>294300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>281600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>278800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>276900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>274000</v>
       </c>
-      <c r="J76" s="3">
-        <v>0</v>
-      </c>
       <c r="K76" s="3">
         <v>0</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
+      <c r="L76" s="3">
+        <v>0</v>
       </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
@@ -3655,8 +3841,11 @@
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3702,43 +3891,46 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3754,37 +3946,40 @@
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E81" s="3">
         <v>1300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>7100</v>
       </c>
-      <c r="J81" s="3">
-        <v>0</v>
-      </c>
       <c r="K81" s="3">
         <v>0</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
+      <c r="L81" s="3">
+        <v>0</v>
       </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
@@ -3801,8 +3996,11 @@
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3820,8 +4018,9 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3867,8 +4066,11 @@
       <c r="Q83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3914,8 +4116,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3961,8 +4166,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4008,8 +4216,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4055,8 +4266,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4102,37 +4316,40 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="E89" s="3">
         <v>-300</v>
       </c>
       <c r="F89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G89" s="3">
         <v>-200</v>
-      </c>
-      <c r="G89" s="3">
-        <v>-100</v>
       </c>
       <c r="H89" s="3">
         <v>-100</v>
       </c>
       <c r="I89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J89" s="3">
         <v>-500</v>
       </c>
-      <c r="J89" s="3">
-        <v>0</v>
-      </c>
       <c r="K89" s="3">
         <v>0</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
+      <c r="L89" s="3">
+        <v>0</v>
       </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
@@ -4149,8 +4366,11 @@
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4168,8 +4388,9 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4215,8 +4436,11 @@
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4262,8 +4486,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4309,17 +4536,20 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E94" s="3">
         <v>258100</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
       <c r="F94" s="3">
         <v>0</v>
       </c>
@@ -4330,11 +4560,11 @@
         <v>0</v>
       </c>
       <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>-293300</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4347,8 +4577,8 @@
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
+      <c r="O94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P94" s="3">
         <v>0</v>
@@ -4356,8 +4586,11 @@
       <c r="Q94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4375,8 +4608,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4422,8 +4656,11 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4469,8 +4706,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4516,8 +4756,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4563,20 +4806,23 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-258100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-100</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
         <v>0</v>
       </c>
@@ -4584,16 +4830,16 @@
         <v>0</v>
       </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>295000</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
         <v>0</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
+      <c r="L100" s="3">
+        <v>0</v>
       </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
@@ -4610,8 +4856,11 @@
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4657,37 +4906,40 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="E102" s="3">
         <v>-300</v>
       </c>
       <c r="F102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G102" s="3">
         <v>-200</v>
-      </c>
-      <c r="G102" s="3">
-        <v>-100</v>
       </c>
       <c r="H102" s="3">
         <v>-100</v>
       </c>
       <c r="I102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J102" s="3">
         <v>1200</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
       <c r="K102" s="3">
         <v>0</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
+      <c r="L102" s="3">
+        <v>0</v>
       </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
@@ -4702,6 +4954,9 @@
         <v>3</v>
       </c>
       <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
